--- a/data/series.xlsx
+++ b/data/series.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marce\Proyectos\juventud-san-rafael\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA5A027D-4D46-4C43-8FAC-F066AF7F5E44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F5DDBFD-EDF6-441A-A8F8-C2173D284B86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Series" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="54">
   <si>
     <t>id</t>
   </si>
@@ -107,9 +107,6 @@
     <t>Valentina Toro</t>
   </si>
   <si>
-    <t>Vicente Aravena</t>
-  </si>
-  <si>
     <t>Tomás Espinoza</t>
   </si>
   <si>
@@ -156,6 +153,36 @@
   </si>
   <si>
     <t>Marcelo Pizarro</t>
+  </si>
+  <si>
+    <t>1Infantil</t>
+  </si>
+  <si>
+    <t>2Infantil</t>
+  </si>
+  <si>
+    <t>3Infantil</t>
+  </si>
+  <si>
+    <t>3Adulto</t>
+  </si>
+  <si>
+    <t>2Adulto</t>
+  </si>
+  <si>
+    <t>1Adulto</t>
+  </si>
+  <si>
+    <t>Sr35</t>
+  </si>
+  <si>
+    <t>Sr45</t>
+  </si>
+  <si>
+    <t>Juan Perez</t>
+  </si>
+  <si>
+    <t>Daniel Muñoz</t>
   </si>
 </sst>
 </file>
@@ -520,114 +547,114 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C5" t="s">
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
         <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C7" t="s">
         <v>4</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C8" t="s">
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -637,7 +664,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -666,7 +693,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -680,7 +707,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B3">
         <v>4</v>
@@ -694,7 +721,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B4">
         <v>5</v>
@@ -708,7 +735,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B5">
         <v>6</v>
@@ -722,7 +749,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B6">
         <v>8</v>
@@ -736,7 +763,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B7">
         <v>9</v>
@@ -750,7 +777,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B8">
         <v>10</v>
@@ -764,7 +791,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B9">
         <v>11</v>
@@ -778,7 +805,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -792,7 +819,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B11">
         <v>3</v>
@@ -806,7 +833,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B12">
         <v>7</v>
@@ -820,7 +847,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B13">
         <v>9</v>
@@ -834,7 +861,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B14">
         <v>10</v>
@@ -848,13 +875,13 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="D15" t="s">
         <v>10</v>
@@ -862,13 +889,13 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B16">
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D16" t="s">
         <v>12</v>
@@ -876,13 +903,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B17">
         <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D17" t="s">
         <v>15</v>
@@ -890,13 +917,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B18">
         <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D18" t="s">
         <v>18</v>
@@ -904,13 +931,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D19" t="s">
         <v>10</v>
@@ -918,13 +945,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B20">
         <v>4</v>
       </c>
       <c r="C20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D20" t="s">
         <v>12</v>
@@ -932,13 +959,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B21">
         <v>8</v>
       </c>
       <c r="C21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D21" t="s">
         <v>15</v>
@@ -946,15 +973,29 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B22">
         <v>9</v>
       </c>
       <c r="C22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23">
+        <v>22</v>
+      </c>
+      <c r="C23" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" t="s">
         <v>18</v>
       </c>
     </row>

--- a/data/series.xlsx
+++ b/data/series.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marce\Proyectos\juventud-san-rafael\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F5DDBFD-EDF6-441A-A8F8-C2173D284B86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A82BC3B-297E-434C-8978-1366600A7D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Series" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="55">
   <si>
     <t>id</t>
   </si>
@@ -183,6 +183,9 @@
   </si>
   <si>
     <t>Daniel Muñoz</t>
+  </si>
+  <si>
+    <t>/jugadores/marcelo-pizarro.jpeg</t>
   </si>
 </sst>
 </file>
@@ -671,7 +674,7 @@
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="19" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="5" max="5" width="27.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -886,6 +889,9 @@
       <c r="D15" t="s">
         <v>10</v>
       </c>
+      <c r="E15" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">

--- a/data/series.xlsx
+++ b/data/series.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marce\Proyectos\juventud-san-rafael\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A82BC3B-297E-434C-8978-1366600A7D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7364927-8A76-499F-9E58-FCA8052C642C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Series" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="56">
   <si>
     <t>id</t>
   </si>
@@ -186,6 +186,9 @@
   </si>
   <si>
     <t>/jugadores/marcelo-pizarro.jpeg</t>
+  </si>
+  <si>
+    <t>Adulto</t>
   </si>
 </sst>
 </file>
@@ -598,7 +601,7 @@
         <v>37</v>
       </c>
       <c r="C5" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
         <v>42</v>
@@ -612,7 +615,7 @@
         <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
         <v>42</v>
@@ -626,7 +629,7 @@
         <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
         <v>42</v>
@@ -640,7 +643,7 @@
         <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="D8" t="s">
         <v>42</v>
@@ -654,7 +657,7 @@
         <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="D9" t="s">
         <v>42</v>

--- a/data/series.xlsx
+++ b/data/series.xlsx
@@ -8,20 +8,33 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marce\Proyectos\juventud-san-rafael\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7364927-8A76-499F-9E58-FCA8052C642C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{363BB1F9-9362-49C6-9078-57D3E9F200B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Series" sheetId="1" r:id="rId1"/>
     <sheet name="Jugadores" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="77">
   <si>
     <t>id</t>
   </si>
@@ -116,15 +129,6 @@
     <t>Bastián Núñez</t>
   </si>
   <si>
-    <t>Patricio Núñez</t>
-  </si>
-  <si>
-    <t>Manuel Bustos</t>
-  </si>
-  <si>
-    <t>Jorge Villalobos</t>
-  </si>
-  <si>
     <t>3ra Infantil</t>
   </si>
   <si>
@@ -179,16 +183,88 @@
     <t>Sr45</t>
   </si>
   <si>
-    <t>Juan Perez</t>
-  </si>
-  <si>
-    <t>Daniel Muñoz</t>
-  </si>
-  <si>
     <t>/jugadores/marcelo-pizarro.jpeg</t>
   </si>
   <si>
     <t>Adulto</t>
+  </si>
+  <si>
+    <t>Hernan Herrera</t>
+  </si>
+  <si>
+    <t>Jose Aleguy</t>
+  </si>
+  <si>
+    <t>Stiven Rodriguez</t>
+  </si>
+  <si>
+    <t>Cristian Silva</t>
+  </si>
+  <si>
+    <t>Gremy Carrasco</t>
+  </si>
+  <si>
+    <t>Alvaro Vasquez</t>
+  </si>
+  <si>
+    <t>Arle Paredes</t>
+  </si>
+  <si>
+    <t>Fabian Rosas</t>
+  </si>
+  <si>
+    <t>Mauricio Vasquez</t>
+  </si>
+  <si>
+    <t>Erick Gonzalez</t>
+  </si>
+  <si>
+    <t>Cristian Gonzalez</t>
+  </si>
+  <si>
+    <t>Ricardo Garrido</t>
+  </si>
+  <si>
+    <t>Marco Uribe</t>
+  </si>
+  <si>
+    <t>Pablo Rubilar</t>
+  </si>
+  <si>
+    <t>Alonso Rivera</t>
+  </si>
+  <si>
+    <t>Rolando Rojas</t>
+  </si>
+  <si>
+    <t>Jesus Vasquez</t>
+  </si>
+  <si>
+    <t>Cristian Jimenez</t>
+  </si>
+  <si>
+    <t>Marco Arevalo</t>
+  </si>
+  <si>
+    <t>Marcos Gallegos</t>
+  </si>
+  <si>
+    <t>Marcelo Palma</t>
+  </si>
+  <si>
+    <t>Rafael Contreras</t>
+  </si>
+  <si>
+    <t>Hector Menares</t>
+  </si>
+  <si>
+    <t>Juan Cartes</t>
+  </si>
+  <si>
+    <t>Ivan Albornoz</t>
+  </si>
+  <si>
+    <t>Jonathan Ortega</t>
   </si>
 </sst>
 </file>
@@ -553,114 +629,114 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" t="s">
         <v>39</v>
-      </c>
-      <c r="C7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D7" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" t="s">
         <v>50</v>
       </c>
-      <c r="B8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" t="s">
-        <v>55</v>
-      </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -670,7 +746,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -699,7 +775,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -713,7 +789,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B3">
         <v>4</v>
@@ -727,7 +803,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B4">
         <v>5</v>
@@ -741,7 +817,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B5">
         <v>6</v>
@@ -755,7 +831,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B6">
         <v>8</v>
@@ -769,7 +845,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B7">
         <v>9</v>
@@ -783,7 +859,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B8">
         <v>10</v>
@@ -797,7 +873,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B9">
         <v>11</v>
@@ -811,7 +887,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -825,7 +901,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B11">
         <v>3</v>
@@ -839,7 +915,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B12">
         <v>7</v>
@@ -853,7 +929,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B13">
         <v>9</v>
@@ -867,7 +943,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B14">
         <v>10</v>
@@ -881,24 +957,24 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D15" t="s">
         <v>10</v>
       </c>
       <c r="E15" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B16">
         <v>5</v>
@@ -912,7 +988,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B17">
         <v>8</v>
@@ -926,7 +1002,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B18">
         <v>11</v>
@@ -940,13 +1016,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D19" t="s">
         <v>10</v>
@@ -954,57 +1030,276 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" t="s">
         <v>51</v>
       </c>
-      <c r="B20">
-        <v>4</v>
-      </c>
-      <c r="C20" t="s">
-        <v>31</v>
-      </c>
       <c r="D20" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>51</v>
-      </c>
-      <c r="B21">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="D21" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>51</v>
-      </c>
-      <c r="B22">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="D22" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>51</v>
-      </c>
-      <c r="B23">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" t="s">
+        <v>61</v>
+      </c>
+      <c r="D30" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31" t="s">
+        <v>62</v>
+      </c>
+      <c r="D31" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32" t="s">
+        <v>63</v>
+      </c>
+      <c r="D32" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>48</v>
+      </c>
+      <c r="C33" t="s">
+        <v>64</v>
+      </c>
+      <c r="D33" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>48</v>
+      </c>
+      <c r="C34" t="s">
+        <v>65</v>
+      </c>
+      <c r="D34" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>48</v>
+      </c>
+      <c r="C35" t="s">
+        <v>66</v>
+      </c>
+      <c r="D35" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>48</v>
+      </c>
+      <c r="C36" t="s">
+        <v>67</v>
+      </c>
+      <c r="D36" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>48</v>
+      </c>
+      <c r="C37" t="s">
+        <v>68</v>
+      </c>
+      <c r="D37" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>48</v>
+      </c>
+      <c r="C38" t="s">
+        <v>69</v>
+      </c>
+      <c r="D38" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>48</v>
+      </c>
+      <c r="C39" t="s">
+        <v>70</v>
+      </c>
+      <c r="D39" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>48</v>
+      </c>
+      <c r="C40" t="s">
+        <v>71</v>
+      </c>
+      <c r="D40" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>48</v>
+      </c>
+      <c r="C41" t="s">
+        <v>72</v>
+      </c>
+      <c r="D41" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>48</v>
+      </c>
+      <c r="C42" t="s">
+        <v>73</v>
+      </c>
+      <c r="D42" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>48</v>
+      </c>
+      <c r="C43" t="s">
+        <v>74</v>
+      </c>
+      <c r="D43" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>48</v>
+      </c>
+      <c r="C44" t="s">
+        <v>75</v>
+      </c>
+      <c r="D44" t="s">
         <v>18</v>
       </c>
     </row>

--- a/data/series.xlsx
+++ b/data/series.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marce\Proyectos\juventud-san-rafael\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{363BB1F9-9362-49C6-9078-57D3E9F200B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F77C977F-C7D3-4243-B8C8-8734AFC33C63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="85">
   <si>
     <t>id</t>
   </si>
@@ -63,72 +63,18 @@
     <t>foto</t>
   </si>
   <si>
-    <t>Ignacio Rojas</t>
-  </si>
-  <si>
     <t>Arquero</t>
   </si>
   <si>
-    <t>Benjamín Silva</t>
-  </si>
-  <si>
     <t>Defensa</t>
   </si>
   <si>
-    <t>Cristóbal Muñoz</t>
-  </si>
-  <si>
-    <t>Diego Contreras</t>
-  </si>
-  <si>
     <t>Mediocampista</t>
   </si>
   <si>
-    <t>Matías Herrera</t>
-  </si>
-  <si>
-    <t>Joaquín Torres</t>
-  </si>
-  <si>
     <t>Delantero</t>
   </si>
   <si>
-    <t>Felipe Araya</t>
-  </si>
-  <si>
-    <t>Sebastián Vega</t>
-  </si>
-  <si>
-    <t>Antonia Reyes</t>
-  </si>
-  <si>
-    <t>Arquera</t>
-  </si>
-  <si>
-    <t>Florencia Bravo</t>
-  </si>
-  <si>
-    <t>Isidora Campos</t>
-  </si>
-  <si>
-    <t>Camila Soto</t>
-  </si>
-  <si>
-    <t>Delantera</t>
-  </si>
-  <si>
-    <t>Valentina Toro</t>
-  </si>
-  <si>
-    <t>Tomás Espinoza</t>
-  </si>
-  <si>
-    <t>Agustín Ramírez</t>
-  </si>
-  <si>
-    <t>Bastián Núñez</t>
-  </si>
-  <si>
     <t>3ra Infantil</t>
   </si>
   <si>
@@ -265,6 +211,84 @@
   </si>
   <si>
     <t>Jonathan Ortega</t>
+  </si>
+  <si>
+    <t>Alexis Alegría</t>
+  </si>
+  <si>
+    <t>Daniel Muñoz</t>
+  </si>
+  <si>
+    <t>Jonathan Vasquez</t>
+  </si>
+  <si>
+    <t>Sergio Moscoso</t>
+  </si>
+  <si>
+    <t>David Ceballo</t>
+  </si>
+  <si>
+    <t>Smiljan Becerra</t>
+  </si>
+  <si>
+    <t>Alvaro Jaque</t>
+  </si>
+  <si>
+    <t>Francisco Araya</t>
+  </si>
+  <si>
+    <t>Emerson Castro</t>
+  </si>
+  <si>
+    <t>Maximiliano Armijo</t>
+  </si>
+  <si>
+    <t>Ariel Nicolao</t>
+  </si>
+  <si>
+    <t>Sebastián Fuentes</t>
+  </si>
+  <si>
+    <t>Cristian Lara</t>
+  </si>
+  <si>
+    <t>Marco Castillo</t>
+  </si>
+  <si>
+    <t>Juan Carlos Catalan</t>
+  </si>
+  <si>
+    <t>Ariel Bustamante</t>
+  </si>
+  <si>
+    <t>Angelo Soto</t>
+  </si>
+  <si>
+    <t>Dean Castillo</t>
+  </si>
+  <si>
+    <t>Christian López</t>
+  </si>
+  <si>
+    <t>Jerson Constanzo</t>
+  </si>
+  <si>
+    <t>Juan Pablo Martínez</t>
+  </si>
+  <si>
+    <t>Carlos Navarro</t>
+  </si>
+  <si>
+    <t>Victor Huera</t>
+  </si>
+  <si>
+    <t>Samuel Campos</t>
+  </si>
+  <si>
+    <t>Emanuel Saavedra</t>
+  </si>
+  <si>
+    <t>Sebastián Guzmán</t>
   </si>
 </sst>
 </file>
@@ -629,114 +653,114 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -746,7 +770,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -775,485 +799,440 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
-        <v>10</v>
+      <c r="E2" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8">
+        <v>29</v>
+      </c>
+      <c r="C8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" t="s">
         <v>10</v>
-      </c>
-      <c r="C8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="D12" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="D14" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>47</v>
-      </c>
-      <c r="B15">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D15" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="D16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="D17" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>47</v>
-      </c>
-      <c r="B18">
+        <v>29</v>
+      </c>
+      <c r="C18" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" t="s">
         <v>11</v>
-      </c>
-      <c r="C18" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>48</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="D19" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C20" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="D20" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C21" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="D21" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="D22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C23" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="D23" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C24" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="D24" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="D25" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C26" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="D26" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C27" t="s">
         <v>58</v>
       </c>
       <c r="D27" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C28" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="D28" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D29" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>30</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="D30" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="C31" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="D31" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D32" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="C33" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="D33" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="C34" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="D34" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="C35" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="D35" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="C36" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D36" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="C37" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="D37" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="C38" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D38" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="C39" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="D39" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="C40" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="D40" t="s">
         <v>12</v>
@@ -1261,49 +1240,163 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="C41" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="D41" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="C42" t="s">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="D42" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="C43" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="D43" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>30</v>
+      </c>
+      <c r="C44" t="s">
+        <v>46</v>
+      </c>
+      <c r="D44" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C45" t="s">
+        <v>47</v>
+      </c>
+      <c r="D45" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>30</v>
+      </c>
+      <c r="C46" t="s">
         <v>48</v>
       </c>
-      <c r="C44" t="s">
-        <v>75</v>
-      </c>
-      <c r="D44" t="s">
-        <v>18</v>
+      <c r="D46" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>30</v>
+      </c>
+      <c r="C47" t="s">
+        <v>49</v>
+      </c>
+      <c r="D47" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>30</v>
+      </c>
+      <c r="C48" t="s">
+        <v>50</v>
+      </c>
+      <c r="D48" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>30</v>
+      </c>
+      <c r="C49" t="s">
+        <v>51</v>
+      </c>
+      <c r="D49" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>30</v>
+      </c>
+      <c r="C50" t="s">
+        <v>52</v>
+      </c>
+      <c r="D50" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>30</v>
+      </c>
+      <c r="C51" t="s">
+        <v>54</v>
+      </c>
+      <c r="D51" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>30</v>
+      </c>
+      <c r="C52" t="s">
+        <v>55</v>
+      </c>
+      <c r="D52" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>30</v>
+      </c>
+      <c r="C53" t="s">
+        <v>56</v>
+      </c>
+      <c r="D53" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>30</v>
+      </c>
+      <c r="C54" t="s">
+        <v>57</v>
+      </c>
+      <c r="D54" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E54">
+    <sortCondition ref="A2:A54"/>
+    <sortCondition ref="D2:D54"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/series.xlsx
+++ b/data/series.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marce\Proyectos\juventud-san-rafael\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F77C977F-C7D3-4243-B8C8-8734AFC33C63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE297FC1-418D-449A-8063-69905375DB2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="87">
   <si>
     <t>id</t>
   </si>
@@ -289,6 +289,12 @@
   </si>
   <si>
     <t>Sebastián Guzmán</t>
+  </si>
+  <si>
+    <t>/jugadores/sebastian-fuentes.jpeg</t>
+  </si>
+  <si>
+    <t>/jugadores/alexis-alegria.jpeg</t>
   </si>
 </sst>
 </file>
@@ -971,7 +977,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -982,7 +988,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -993,7 +999,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>29</v>
       </c>
@@ -1004,7 +1010,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -1015,7 +1021,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -1026,7 +1032,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -1037,7 +1043,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>29</v>
       </c>
@@ -1048,7 +1054,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -1059,7 +1065,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1070,7 +1076,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1081,7 +1087,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -1092,7 +1098,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>29</v>
       </c>
@@ -1102,10 +1108,16 @@
       <c r="D28" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E28" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>29</v>
+      </c>
+      <c r="B29">
+        <v>7</v>
       </c>
       <c r="C29" t="s">
         <v>59</v>
@@ -1113,8 +1125,11 @@
       <c r="D29" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E29" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>30</v>
       </c>
@@ -1128,7 +1143,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -1139,7 +1154,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>30</v>
       </c>
